--- a/hardware/devBoard/manufacture/devBoard CPL.xlsx
+++ b/hardware/devBoard/manufacture/devBoard CPL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\Manufacturing Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D848169-DD91-4FB7-A8F9-1A5A15D7ACF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A600E33-5176-4C55-BC69-2FF82E9F276F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1783,7 +1783,7 @@
         <v>62</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
